--- a/day20_FE_AT/Automation_Test_Report.xlsx
+++ b/day20_FE_AT/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="231">
   <si>
     <t>Project name:</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Project Assigned Date:</t>
   </si>
   <si>
-    <t>2026-07-17</t>
+    <t>2026-07-18</t>
   </si>
   <si>
     <t>Module Name:</t>
@@ -610,6 +610,129 @@
   </si>
   <si>
     <t>As Expected: Ticket status filters successfully isolated Open and Resolved cases.</t>
+  </si>
+  <si>
+    <t>TC#27</t>
+  </si>
+  <si>
+    <t>Validate incorrect login attempts are rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to login page.
+2. Input nonexistent@corptech.com and submit, verify account error.
+3. Input admin@corptech.com and invalid password, verify password error.</t>
+  </si>
+  <si>
+    <t>Emails: nonexistent@corptech.com / admin@corptech.com | Passwords: employee123 / wrongpassword</t>
+  </si>
+  <si>
+    <t>Login attempts are blocked with appropriate validation error messages.</t>
+  </si>
+  <si>
+    <t>As Expected: Invalid login attempts were rejected with correct error message alerts.</t>
+  </si>
+  <si>
+    <t>TC#28</t>
+  </si>
+  <si>
+    <t>Delete newly created employee record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search directory for 'EndToEnd' record.
+2. Click delete button, wait for confirmation modal overlay.
+3. Confirm deletion by clicking Yes, Delete Record.
+4. Search directory again, verify record is removed.</t>
+  </si>
+  <si>
+    <t>Roster search: EndToEnd</t>
+  </si>
+  <si>
+    <t>Roster record is deleted and is no longer found in local list search.</t>
+  </si>
+  <si>
+    <t>As Expected: Employee record successfully deleted and confirmed absent from directory.</t>
+  </si>
+  <si>
+    <t>TC#29</t>
+  </si>
+  <si>
+    <t>Navigate Department Hub overview and check detail roster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Department Hub link in sidebar.
+2. Click QA &amp; Testing department card.
+3. Assert Active Roster loads with assigned team members.
+4. Click Back to Overview to return to department cards.</t>
+  </si>
+  <si>
+    <t>Department target: QA &amp; Testing</t>
+  </si>
+  <si>
+    <t>Detail view opens, displays roster list, and back button successfully returns to overview.</t>
+  </si>
+  <si>
+    <t>As Expected: Department Hub loaded card overview and rendered detail roster correctly.</t>
+  </si>
+  <si>
+    <t>TC#30</t>
+  </si>
+  <si>
+    <t>Verify learning page compliance rates and audit badge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Learning &amp; Compliance link in sidebar.
+2. Verify Corporate Compliance Rate progress displays.
+3. Verify Passed Compliance Audit status badge is visible.</t>
+  </si>
+  <si>
+    <t>Learning &amp; Compliance dashboard elements</t>
+  </si>
+  <si>
+    <t>Compliance overview displays progress indicators and status clearance badge.</t>
+  </si>
+  <si>
+    <t>As Expected: Learning compliance panel loaded rates and audit clearance status.</t>
+  </si>
+  <si>
+    <t>TC#31</t>
+  </si>
+  <si>
+    <t>Navigate to dedicated Performance reviews management page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Performance link in sidebar.
+2. Verify Average Rating stats card is displayed.
+3. Verify employee evaluations table renders with action buttons.</t>
+  </si>
+  <si>
+    <t>Admin Performance management panel</t>
+  </si>
+  <si>
+    <t>Reviews manager dashboard loads metrics and roster for evaluation.</t>
+  </si>
+  <si>
+    <t>As Expected: Performance manager view loaded stats and employee reviews table.</t>
+  </si>
+  <si>
+    <t>TC#32</t>
+  </si>
+  <si>
+    <t>Update profile contact info and verify password change validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Profile Settings link in sidebar.
+2. Input new phone number and click Save, verify success alert.
+3. Input blank fields or unmatched passwords in Security, verify error alert.
+4. Save valid password change, verify success message.</t>
+  </si>
+  <si>
+    <t>Phone: +1 (555) 999-8888 | Password update validation</t>
+  </si>
+  <si>
+    <t>Contact details update successfully, and password validations block incorrect inputs.</t>
+  </si>
+  <si>
+    <t>As Expected: Contact info updated and password change validations performed successfully.</t>
   </si>
   <si>
     <t>Facebook Login Sanity &amp; Employee Workspace (Helpdesk / Compliance)</t>
@@ -1114,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1807,6 +1930,144 @@
         <v>178</v>
       </c>
       <c r="G36" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G42" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1874,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1921,19 +2182,19 @@
         <v>22</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>28</v>
@@ -1944,19 +2205,19 @@
         <v>29</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>28</v>
@@ -1967,19 +2228,19 @@
         <v>35</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>28</v>

--- a/day20_FE_AT/Automation_Test_Report.xlsx
+++ b/day20_FE_AT/Automation_Test_Report.xlsx
@@ -4,15 +4,28 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="TestNG E2E Portal" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Cucumber BDD Workspace" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Authentication" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Employee Directory" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Employee Form" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Navigation" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Announcements" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Attendance" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Performance" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Leave Management" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Permissions" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="IT Assets" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Helpdesk Tickets" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Department Hub" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Learning &amp; Compliance" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Profile Settings" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="BDD Integration" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="244">
   <si>
     <t>Project name:</t>
   </si>
@@ -47,7 +60,7 @@
     <t>Module Name:</t>
   </si>
   <si>
-    <t>Employee Directory, Pay Analytics, Access Control &amp; Live API Integration</t>
+    <t>Authentication</t>
   </si>
   <si>
     <t>End Date:</t>
@@ -125,6 +138,29 @@
     <t>As Expected: Admin welcomes Nijay V successfully.</t>
   </si>
   <si>
+    <t>TC#27</t>
+  </si>
+  <si>
+    <t>Validate incorrect login attempts are rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to login page.
+2. Input nonexistent@corptech.com and submit, verify account error.
+3. Input admin@corptech.com and invalid password, verify password error.</t>
+  </si>
+  <si>
+    <t>Emails: nonexistent@corptech.com / admin@corptech.com | Passwords: employee123 / wrongpassword</t>
+  </si>
+  <si>
+    <t>Login attempts are blocked with appropriate validation error messages.</t>
+  </si>
+  <si>
+    <t>As Expected: Invalid login attempts were rejected with correct error message alerts.</t>
+  </si>
+  <si>
+    <t>Employee Directory</t>
+  </si>
+  <si>
     <t>TC#3</t>
   </si>
   <si>
@@ -147,6 +183,148 @@
     <t>As Expected: Search isolated target record, and custom dropdown filtered Engineering department.</t>
   </si>
   <si>
+    <t>TC#10</t>
+  </si>
+  <si>
+    <t>Filter employee roster by Inactive (Suspended) status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Status custom dropdown trigger.
+2. Select 'Suspended' option.
+3. Verify all visible employee rows display Suspended status badge.</t>
+  </si>
+  <si>
+    <t>Status: Suspended</t>
+  </si>
+  <si>
+    <t>Roster matches filter and shows only Suspended employees.</t>
+  </si>
+  <si>
+    <t>As Expected: Roster filtered only Suspended status successfully.</t>
+  </si>
+  <si>
+    <t>TC#11</t>
+  </si>
+  <si>
+    <t>Filter employee roster by On Leave status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Status custom dropdown trigger.
+2. Select 'On Leave' option.
+3. Verify all visible employee rows display On Leave status badge.</t>
+  </si>
+  <si>
+    <t>Status: On Leave</t>
+  </si>
+  <si>
+    <t>Roster matches filter and shows only On Leave employees.</t>
+  </si>
+  <si>
+    <t>As Expected: Roster filtered only On Leave status successfully.</t>
+  </si>
+  <si>
+    <t>TC#12</t>
+  </si>
+  <si>
+    <t>Open employee drawer general profile information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click an employee name in the directory roster table.
+2. Assert detail drawer slide-out animation occurs.
+3. Confirm ID, email, joining date, and tenure display.</t>
+  </si>
+  <si>
+    <t>Employee ID: 1 (Nijay V)</t>
+  </si>
+  <si>
+    <t>Employee drawer displays core profile information for selected record.</t>
+  </si>
+  <si>
+    <t>As Expected: General profile fields populated in drawer.</t>
+  </si>
+  <si>
+    <t>TC#13</t>
+  </si>
+  <si>
+    <t>Open employee drawer leaves and attendance tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click employee name and click 'Leaves' tab inside drawer.
+2. Verify Time Off Requests section header is visible.</t>
+  </si>
+  <si>
+    <t>Tab selection: Leaves</t>
+  </si>
+  <si>
+    <t>Drawer displays history list of time off requests.</t>
+  </si>
+  <si>
+    <t>As Expected: Time Off history tab loaded inside employee detail drawer.</t>
+  </si>
+  <si>
+    <t>TC#14</t>
+  </si>
+  <si>
+    <t>Open employee drawer performance review tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click employee name and click 'Performance' tab inside drawer.
+2. Verify Performance Review section header is visible.</t>
+  </si>
+  <si>
+    <t>Tab selection: Performance</t>
+  </si>
+  <si>
+    <t>Drawer displays performance scores, ratings, and comments.</t>
+  </si>
+  <si>
+    <t>As Expected: Performance review tab loaded inside employee detail drawer.</t>
+  </si>
+  <si>
+    <t>TC#15</t>
+  </si>
+  <si>
+    <t>Edit employee designation and save update</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search for employee, click Edit Employee button to open modal.
+2. Change Role selection dropdown to 'Product Manager'.
+3. Save form, assert table displays updated role for employee.</t>
+  </si>
+  <si>
+    <t>Employee: Nijay | New Role: Product Manager</t>
+  </si>
+  <si>
+    <t>Designation update successfully saves and updates directory list.</t>
+  </si>
+  <si>
+    <t>As Expected: Employee role updated to Product Manager in roster.</t>
+  </si>
+  <si>
+    <t>TC#28</t>
+  </si>
+  <si>
+    <t>Delete newly created employee record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search directory for 'EndToEnd' record.
+2. Click delete button, wait for confirmation modal overlay.
+3. Confirm deletion by clicking Yes, Delete Record.
+4. Search directory again, verify record is removed.</t>
+  </si>
+  <si>
+    <t>Roster search: EndToEnd</t>
+  </si>
+  <si>
+    <t>Roster record is deleted and is no longer found in local list search.</t>
+  </si>
+  <si>
+    <t>As Expected: Employee record successfully deleted and confirmed absent from directory.</t>
+  </si>
+  <si>
+    <t>Employee Form</t>
+  </si>
+  <si>
     <t>TC#4</t>
   </si>
   <si>
@@ -168,6 +346,9 @@
     <t>As Expected: Validations flagged malformed input, and valid analyst record saved.</t>
   </si>
   <si>
+    <t>Navigation</t>
+  </si>
+  <si>
     <t>TC#5</t>
   </si>
   <si>
@@ -186,6 +367,9 @@
   </si>
   <si>
     <t>As Expected: Pay Analytics and Permissions modules loaded with active class indicators.</t>
+  </si>
+  <si>
+    <t>Announcements</t>
   </si>
   <si>
     <t>TC#6</t>
@@ -209,6 +393,29 @@
     <t>As Expected: Announcements board bulletin successfully published and deleted.</t>
   </si>
   <si>
+    <t>TC#19</t>
+  </si>
+  <si>
+    <t>Validate empty announcement form block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Announcements Board.
+2. Click Publish without entering title or content.
+3. Verify submit is blocked (fields remain visible).</t>
+  </si>
+  <si>
+    <t>Title: blank | Content: blank</t>
+  </si>
+  <si>
+    <t>Form submission is blocked for empty announcement notice.</t>
+  </si>
+  <si>
+    <t>As Expected: Empty announcement publication blocked successfully.</t>
+  </si>
+  <si>
+    <t>Attendance</t>
+  </si>
+  <si>
     <t>TC#7</t>
   </si>
   <si>
@@ -227,6 +434,9 @@
   </si>
   <si>
     <t>As Expected: Calendar rendered grid cells populated with shift statuses.</t>
+  </si>
+  <si>
+    <t>Performance</t>
   </si>
   <si>
     <t>TC#8</t>
@@ -251,6 +461,29 @@
     <t>As Expected: Updated performance details (4.7 rating, 85% OKR) successfully synced.</t>
   </si>
   <si>
+    <t>TC#31</t>
+  </si>
+  <si>
+    <t>Navigate to dedicated Performance reviews management page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Performance link in sidebar.
+2. Verify Average Rating stats card is displayed.
+3. Verify employee evaluations table renders with action buttons.</t>
+  </si>
+  <si>
+    <t>Admin Performance management panel</t>
+  </si>
+  <si>
+    <t>Reviews manager dashboard loads metrics and roster for evaluation.</t>
+  </si>
+  <si>
+    <t>As Expected: Performance manager view loaded stats and employee reviews table.</t>
+  </si>
+  <si>
+    <t>Leave Management</t>
+  </si>
+  <si>
     <t>TC#9</t>
   </si>
   <si>
@@ -273,122 +506,47 @@
     <t>As Expected: Employee leave request approved by admin with remarks synced.</t>
   </si>
   <si>
-    <t>TC#10</t>
-  </si>
-  <si>
-    <t>Filter employee roster by Inactive (Suspended) status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Status custom dropdown trigger.
-2. Select 'Suspended' option.
-3. Verify all visible employee rows display Suspended status badge.</t>
-  </si>
-  <si>
-    <t>Status: Suspended</t>
-  </si>
-  <si>
-    <t>Roster matches filter and shows only Suspended employees.</t>
-  </si>
-  <si>
-    <t>As Expected: Roster filtered only Suspended status successfully.</t>
-  </si>
-  <si>
-    <t>TC#11</t>
-  </si>
-  <si>
-    <t>Filter employee roster by On Leave status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Status custom dropdown trigger.
-2. Select 'On Leave' option.
-3. Verify all visible employee rows display On Leave status badge.</t>
-  </si>
-  <si>
-    <t>Status: On Leave</t>
-  </si>
-  <si>
-    <t>Roster matches filter and shows only On Leave employees.</t>
-  </si>
-  <si>
-    <t>As Expected: Roster filtered only On Leave status successfully.</t>
-  </si>
-  <si>
-    <t>TC#12</t>
-  </si>
-  <si>
-    <t>Open employee drawer general profile information</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click an employee name in the directory roster table.
-2. Assert detail drawer slide-out animation occurs.
-3. Confirm ID, email, joining date, and tenure display.</t>
-  </si>
-  <si>
-    <t>Employee ID: 1 (Nijay V)</t>
-  </si>
-  <si>
-    <t>Employee drawer displays core profile information for selected record.</t>
-  </si>
-  <si>
-    <t>As Expected: General profile fields populated in drawer.</t>
-  </si>
-  <si>
-    <t>TC#13</t>
-  </si>
-  <si>
-    <t>Open employee drawer leaves and attendance tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click employee name and click 'Leaves' tab inside drawer.
-2. Verify Time Off Requests section header is visible.</t>
-  </si>
-  <si>
-    <t>Tab selection: Leaves</t>
-  </si>
-  <si>
-    <t>Drawer displays history list of time off requests.</t>
-  </si>
-  <si>
-    <t>As Expected: Time Off history tab loaded inside employee detail drawer.</t>
-  </si>
-  <si>
-    <t>TC#14</t>
-  </si>
-  <si>
-    <t>Open employee drawer performance review tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click employee name and click 'Performance' tab inside drawer.
-2. Verify Performance Review section header is visible.</t>
-  </si>
-  <si>
-    <t>Tab selection: Performance</t>
-  </si>
-  <si>
-    <t>Drawer displays performance scores, ratings, and comments.</t>
-  </si>
-  <si>
-    <t>As Expected: Performance review tab loaded inside employee detail drawer.</t>
-  </si>
-  <si>
-    <t>TC#15</t>
-  </si>
-  <si>
-    <t>Edit employee designation and save update</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Search for employee, click Edit Employee button to open modal.
-2. Change Role selection dropdown to 'Product Manager'.
-3. Save form, assert table displays updated role for employee.</t>
-  </si>
-  <si>
-    <t>Employee: Nijay | New Role: Product Manager</t>
-  </si>
-  <si>
-    <t>Designation update successfully saves and updates directory list.</t>
-  </si>
-  <si>
-    <t>As Expected: Employee role updated to Product Manager in roster.</t>
+    <t>TC#17</t>
+  </si>
+  <si>
+    <t>Validate end date cannot be prior to start date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Request Time Off modal.
+2. Set start date to 2026-07-25 and end date to 2026-07-20.
+3. Click Submit and verify validation warning.</t>
+  </si>
+  <si>
+    <t>Start: 2026-07-25 | End: 2026-07-20</t>
+  </si>
+  <si>
+    <t>Form displays error 'End date cannot be prior to start date.'.</t>
+  </si>
+  <si>
+    <t>As Expected: Prior end-date was blocked with correct warning message.</t>
+  </si>
+  <si>
+    <t>TC#18</t>
+  </si>
+  <si>
+    <t>Validate leave request requires all fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Request Time Off modal.
+2. Click Submit without filling dates or reason.
+3. Verify required fields warning is shown.</t>
+  </si>
+  <si>
+    <t>Dates: blank | Reason: blank</t>
+  </si>
+  <si>
+    <t>Form displays error 'All fields are required.'.</t>
+  </si>
+  <si>
+    <t>As Expected: Submit blocked with required fields warning.</t>
+  </si>
+  <si>
+    <t>Permissions</t>
   </si>
   <si>
     <t>TC#16</t>
@@ -411,64 +569,7 @@
     <t>As Expected: Permission checkboxes toggled successfully.</t>
   </si>
   <si>
-    <t>TC#17</t>
-  </si>
-  <si>
-    <t>Validate end date cannot be prior to start date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open Request Time Off modal.
-2. Set start date to 2026-07-25 and end date to 2026-07-20.
-3. Click Submit and verify validation warning.</t>
-  </si>
-  <si>
-    <t>Start: 2026-07-25 | End: 2026-07-20</t>
-  </si>
-  <si>
-    <t>Form displays error 'End date cannot be prior to start date.'.</t>
-  </si>
-  <si>
-    <t>As Expected: Prior end-date was blocked with correct warning message.</t>
-  </si>
-  <si>
-    <t>TC#18</t>
-  </si>
-  <si>
-    <t>Validate leave request requires all fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open Request Time Off modal.
-2. Click Submit without filling dates or reason.
-3. Verify required fields warning is shown.</t>
-  </si>
-  <si>
-    <t>Dates: blank | Reason: blank</t>
-  </si>
-  <si>
-    <t>Form displays error 'All fields are required.'.</t>
-  </si>
-  <si>
-    <t>As Expected: Submit blocked with required fields warning.</t>
-  </si>
-  <si>
-    <t>TC#19</t>
-  </si>
-  <si>
-    <t>Validate empty announcement form block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open Announcements Board.
-2. Click Publish without entering title or content.
-3. Verify submit is blocked (fields remain visible).</t>
-  </si>
-  <si>
-    <t>Title: blank | Content: blank</t>
-  </si>
-  <si>
-    <t>Form submission is blocked for empty announcement notice.</t>
-  </si>
-  <si>
-    <t>As Expected: Empty announcement publication blocked successfully.</t>
+    <t>IT Assets</t>
   </si>
   <si>
     <t>TC#20</t>
@@ -529,6 +630,9 @@
   </si>
   <si>
     <t>As Expected: Hardware request rejected and status updated successfully.</t>
+  </si>
+  <si>
+    <t>Helpdesk Tickets</t>
   </si>
   <si>
     <t>TC#23</t>
@@ -612,45 +716,7 @@
     <t>As Expected: Ticket status filters successfully isolated Open and Resolved cases.</t>
   </si>
   <si>
-    <t>TC#27</t>
-  </si>
-  <si>
-    <t>Validate incorrect login attempts are rejected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to login page.
-2. Input nonexistent@corptech.com and submit, verify account error.
-3. Input admin@corptech.com and invalid password, verify password error.</t>
-  </si>
-  <si>
-    <t>Emails: nonexistent@corptech.com / admin@corptech.com | Passwords: employee123 / wrongpassword</t>
-  </si>
-  <si>
-    <t>Login attempts are blocked with appropriate validation error messages.</t>
-  </si>
-  <si>
-    <t>As Expected: Invalid login attempts were rejected with correct error message alerts.</t>
-  </si>
-  <si>
-    <t>TC#28</t>
-  </si>
-  <si>
-    <t>Delete newly created employee record</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Search directory for 'EndToEnd' record.
-2. Click delete button, wait for confirmation modal overlay.
-3. Confirm deletion by clicking Yes, Delete Record.
-4. Search directory again, verify record is removed.</t>
-  </si>
-  <si>
-    <t>Roster search: EndToEnd</t>
-  </si>
-  <si>
-    <t>Roster record is deleted and is no longer found in local list search.</t>
-  </si>
-  <si>
-    <t>As Expected: Employee record successfully deleted and confirmed absent from directory.</t>
+    <t>Department Hub</t>
   </si>
   <si>
     <t>TC#29</t>
@@ -674,6 +740,9 @@
     <t>As Expected: Department Hub loaded card overview and rendered detail roster correctly.</t>
   </si>
   <si>
+    <t>Learning &amp; Compliance</t>
+  </si>
+  <si>
     <t>TC#30</t>
   </si>
   <si>
@@ -694,24 +763,7 @@
     <t>As Expected: Learning compliance panel loaded rates and audit clearance status.</t>
   </si>
   <si>
-    <t>TC#31</t>
-  </si>
-  <si>
-    <t>Navigate to dedicated Performance reviews management page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Performance link in sidebar.
-2. Verify Average Rating stats card is displayed.
-3. Verify employee evaluations table renders with action buttons.</t>
-  </si>
-  <si>
-    <t>Admin Performance management panel</t>
-  </si>
-  <si>
-    <t>Reviews manager dashboard loads metrics and roster for evaluation.</t>
-  </si>
-  <si>
-    <t>As Expected: Performance manager view loaded stats and employee reviews table.</t>
+    <t>Profile Settings</t>
   </si>
   <si>
     <t>TC#32</t>
@@ -735,7 +787,7 @@
     <t>As Expected: Contact info updated and password change validations performed successfully.</t>
   </si>
   <si>
-    <t>Facebook Login Sanity &amp; Employee Workspace (Helpdesk / Compliance)</t>
+    <t>BDD Integration</t>
   </si>
   <si>
     <t>JUnit Integration Sanity Check</t>
@@ -1237,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1381,7 +1433,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>35</v>
       </c>
@@ -1401,673 +1453,6 @@
         <v>40</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="G42" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2077,7 +1462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2135,7 +1520,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2177,24 +1562,784 @@
         <v>21</v>
       </c>
     </row>
+    <row r="11" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="11" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>28</v>
@@ -2205,19 +2350,19 @@
         <v>29</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>28</v>
@@ -2225,24 +2370,1309 @@
     </row>
     <row r="13" ht="108" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="G13" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>28</v>
       </c>
     </row>
